--- a/www/download/COUNTRY.SWE.EXI382.xlsx
+++ b/www/download/COUNTRY.SWE.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Suécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4708</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.995</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4.203</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4.139</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>4.063</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3.987</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.206</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.286</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.492</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.502</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.505</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.462</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.478</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.571</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.68</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.572</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.484</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.511</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.604</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.631</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.624</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>4.378</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4.404</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>4.254</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4.242</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>4.213</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>4.154</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3.954</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.537</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.685</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3.632</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3.586</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3.524</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.722</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.808</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4.01</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>4.017</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>4.035</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3.992</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3.993</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>4.183</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4.095</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>4.005</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>4.016</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>4.125</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>4.147</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>4.143</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>3.924</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3.946</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>3.799</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3.776</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>3.696</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3.508</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7598.077</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>7501.044</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>7472.931</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>7766.793</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>7247.423</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>8082.817</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8273.316</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8179.094</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>8281.619</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>8089.403</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>8116.307</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>8426.406</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>8579.604</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>8780.299</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>8571.183</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>8306.362</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>8504.72</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>8661.381</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>8678.845</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>8673.975</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>8234.389</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8312.344</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>8053.287</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>8065.106</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>8026.416</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>7941.661</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>7590.201</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6597.374</t>
+          <t>18924770147.5264</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5340.792</t>
+          <t>9095064649.35671</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5318.837</t>
+          <t>8791946655.7474</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5616.757</t>
+          <t>9262020785.82598</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5247.205</t>
+          <t>8995497423.76662</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5928.309</t>
+          <t>10376908828.3959</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6097.03</t>
+          <t>10219474359.4682</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6078.812</t>
+          <t>10014145123.165</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6161.091</t>
+          <t>9698471835.79372</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6065.125</t>
+          <t>10406480332.1102</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6073.625</t>
+          <t>10805406991.4911</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6247.562</t>
+          <t>10998407906.6884</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6373.822</t>
+          <t>10679625641.2615</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6570.317</t>
+          <t>11080322687.8374</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6464.209</t>
+          <t>9779581872.10594</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>6247.544</t>
+          <t>9439841724.8212</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>6353.07</t>
+          <t>10547925423.7157</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6576.149</t>
+          <t>10367012669.1204</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>6599.813</t>
+          <t>10345290760.9526</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>7641.162</t>
+          <t>9788793804.03155</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>7259.067</t>
+          <t>9345938222.25205</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7327.497</t>
+          <t>9033510755.72024</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>7073.056</t>
+          <t>8445830700.65372</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7059.694</t>
+          <t>8493461015.43076</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>7031.225</t>
+          <t>8295588469.00564</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>6957.5</t>
+          <t>8628683580.38796</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>6625.671</t>
+          <t>9085784380.48797</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>17433274046.59</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5460776613.843</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>5087874791.02045</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5259858345.19279</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>5423362499.59459</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6118364992.25006</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6718680564.27086</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6813260621.81017</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6175384589.61224</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6009601183.68364</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6164857613.61468</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6021793784.18957</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5486679665.84728</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6310177263.26842</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5580341385.96677</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5075888636.43232</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5821587796.76332</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>6173640387.42372</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>5946555062.06949</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>6044004824.0909</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>6143472241.51084</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5946047415.58871</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>5471072504.41168</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6702629236.41513</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>6564916041.60221</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>6526062974.14149</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>6890484171.42579</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>243621742.902258</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>19991454508738.9</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4611670.37539351</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5399492.13661448</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>876829145.967606</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4150755.50449242</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4362518.16643208</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>290519764.043073</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3807827.95848382</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>604164373.682605</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3449196.86159492</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>827354663.128819</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3207020.97516109</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3282522.89718737</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3671447.82332148</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2692743.55757112</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2681308.42556357</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2607754.89107665</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2624248.01729781</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2615502.3617215</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2512455.29218814</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2211136.51551994</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2383370.53688255</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1957811.77925711</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1792220.73597953</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>1924437.89540058</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2117232.01808648</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16216.1012350291</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>34711.6643196869</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>37906.2810044134</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>39639.434186122</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>38353.8764648688</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>51597.206989708</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>52114.9485712985</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>49168.8987349637</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>45592.283945936</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>43691.3372318353</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>46855.1368284224</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>51494.443132875</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>54041.3474142226</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>55111.831236771</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>54318.1227119598</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>59935.4952047569</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>63930.1353530134</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>71424.997620439</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>69603.2328912996</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>71260.8559369609</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>77216.4884239197</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>71148.872996985</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>72526.9567830769</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>71729.8297027107</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>75450.1655020536</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>72256.3319352377</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>68731.1213940481</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>70544.0231923903</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>69114.0550226058</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>72767.6368634095</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>78809.9886007661</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>80737.241669212</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>111331.91920989</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>110091.857551685</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>104574.079479055</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>93035.3217017888</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>97554.735966768</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>108591.874217701</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>118236.293418899</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>118948.732179868</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>124005.536941738</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>109679.468852329</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>122088.868877774</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>142020.545875972</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>154067.794562078</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>150182.371299877</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>147088.75363494</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>158639.330535607</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>139761.399505659</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>138149.218376148</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>135117.839777081</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>140609.152231717</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>139132.837525029</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>143833.96482523</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.62156423958519</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.0219720787586395</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.0453946330176209</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.0678532826139386</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.0324812327422411</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.0310631994805558</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.0925256913648537</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.107796936382906</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.00231460719669285</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.00923918486748798</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.0147988192647006</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.0374918544041927</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.16169020029979</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.0412254245605588</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.158389523669085</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.230827633836974</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0912950593194803</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.0651979362770452</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.109854853963881</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.264254815118943</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.181590271116963</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.232330801452771</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.292809820159505</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.0532723000341213</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.0710304053764934</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.0661098786493333</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.0384316545913638</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4928.40320200532</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1481.77261385595</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1400.84658343116</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1466.81679500051</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1539.06649060499</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1643.970495271</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1764.26673080997</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1699.23698668427</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1537.27429977182</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1489.25759762164</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1544.38038318909</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1508.23868761978</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1344.74146855355</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1508.38486954812</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1362.58763148121</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1267.45121764666</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1449.59855497086</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1496.78523673174</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1433.87226612433</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1458.8804943544</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1565.61297866305</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1506.77846996812</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1440.27883095967</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1775.12381188604</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1750.7576011576</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1765.54593771722</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1964.38420928554</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>34488113990.3579</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>8481638813.61683</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>8351714873.07486</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>8616314454.5977</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>9137710258.61986</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>9203482943.3241</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>8887461962.50557</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>9390057267.81456</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>9429241972.50112</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>11342018600.4948</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>11032780754.9209</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>11349056398.1811</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>9748208564.41792</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>10611636835.4077</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>8914413140.77693</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>9544763850.94712</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>9746901421.34912</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>9560276921.88162</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>9556227573.02262</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>8743268677.44528</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>8343227292.92712</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>8410512763.07315</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>7078508979.40387</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>7483864237.64953</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>7731187231.60939</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>8340016198.34749</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>8650201830.88405</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>28945234831.6943</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9445122864.51077</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>9308938933.09979</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>9578807520.38527</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>10024395707.2678</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10412394606.4256</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10020237519.1431</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>10044129974.952</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>9782172565.25338</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>11369652922.3715</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>10720477595.3743</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>10661831007.6657</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>8936119737.34157</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>9705141944.80087</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>8221097423.75353</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>8599622406.79292</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>8743092847.41094</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>8416886999.3931</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>8584552245.62732</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>7714253822.17822</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>7314433865.89401</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>7384453033.48466</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>6931464371.39169</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>7418778334.12209</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>7388340955.2684</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>8035231455.88433</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>8657426538.29683</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5542879158.66364</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-963484050.893947</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-957224060.024931</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-962493065.787574</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-886685448.647965</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-1208911663.10152</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1132775556.63754</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-654072707.137477</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-352930592.752252</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-27634321.8766618</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>312303159.546615</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>687225390.515405</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>812088827.076352</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>906494890.606812</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>693315717.023403</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>945141444.154194</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1003808573.93818</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1143389922.48852</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>971675327.395296</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1029014855.26706</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1028793427.03312</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>1026059729.58849</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>147044608.012172</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>65085903.5274385</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>342846276.340985</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>304784742.463161</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-7224707.41277407</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>1865.08401338167</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>1449.21498928191</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>1464.43750000001</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>1566.34512953455</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>1489.07571371786</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>1592.90351183625</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>1601.02673178977</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>1516.06444533118</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>1533.71611361428</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>1503.01712388138</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>1521.52537702233</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1564.78535290279</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>1562.1729859554</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>1570.56867619596</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>1578.4072373889</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>1560.01398321983</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>1581.93974103636</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>1594.3725452166</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>1591.39009452228</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.789</t>
+          <t>1844.39668967066</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>1849.91306392271</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>1856.8495195076</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>1862.00661643252</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>1869.68874019054</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>1875.1146232838</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>1882.26596540953</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>1888.88967386955</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>1902.05759362078</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>1784.60315949756</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>1805.62278010014</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>1911.68479866062</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1817.90026839236</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>1921.91768118756</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>1930.53692684662</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>1820.69185049961</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>1839.37877576424</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>1795.64994450593</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>1819.18794127511</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1881.9023584063</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>1876.92327885963</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1875.97192547632</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>1874.62993744878</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>1852.48600548629</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1885.24561092466</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>1881.39561656934</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>1873.95439725412</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>1875.97396399454</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>1880.98975689642</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>1887.4694475271</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>1893.30930419752</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>1901.12470588184</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>1904.96013392121</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>1911.62791331782</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1919.79613548176</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>79482.544481271</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>91500.0914283411</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>103772.904334647</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>108339.305051303</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>117109.951751735</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>141594.977361391</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>134616.434768766</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>134423.166709013</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>134393.972955574</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>147142.612236066</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>157110.337787187</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>176603.737786454</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>184744.048178004</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>185221.969022886</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>148457.040026664</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>182902.409236707</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>202643.009007068</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>215696.593401901</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>208157.568356573</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>209606.903682642</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>226120.027223574</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>224788.151087574</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>235575.000039661</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>239983.024580083</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>250555.381074289</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>255913.189962297</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>262047.421311451</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4578649118.92703</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2108246322.49888</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2256202584.00421</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2457593119.1216</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2339166756.79365</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2821190228.56306</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2659458699.68453</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2625074717.58782</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2449765224.82569</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2783383199.49166</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2847775152.22044</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2975269884.32104</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2654499653.16576</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3078839685.6987</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2503052409.18639</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2365312758.45693</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2787746403.02014</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2692952025.70859</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2762698663.52376</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2465938710.11239</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2346558218.781</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2239516036.2027</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2303337553.7723</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2302487375.24312</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2359099796.3404</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2518267928.19156</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2557738386.79259</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>64386.0986765711</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>74912.273593845</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>84425.979276515</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>90324.6909188168</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>99200.8259730363</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>122837.120914685</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>116019.503744067</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>114950.249003598</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>113495.520779907</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>119644.976319435</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>131216.008066361</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>146723.472120073</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>156338.957315305</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>159394.801398046</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>126354.749325343</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>157907.943988408</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>177011.800870744</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>188851.500005445</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>183663.881732823</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>188986.416796542</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>203434.223530505</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>206128.321252878</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>219697.484744834</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>226234.063036455</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>228513.145023331</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>234586.495687632</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>240925.378606075</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7598.077</t>
+          <t>30514230434.7378</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7501.044</t>
+          <t>7220268187.08588</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7472.931</t>
+          <t>6986410720.86662</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7766.793</t>
+          <t>7679984526.22583</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7247.423</t>
+          <t>8191557264.91641</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8082.817</t>
+          <t>9114568473.55795</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8273.316</t>
+          <t>8547626436.24115</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8179.094</t>
+          <t>8756659522.33052</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8281.619</t>
+          <t>8328827104.84389</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8089.403</t>
+          <t>9082614703.49491</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8116.307</t>
+          <t>9549714130.84338</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8426.406</t>
+          <t>9878390769.67824</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>8579.604</t>
+          <t>8875295747.90253</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>8780.299</t>
+          <t>10151138271.7357</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>8571.183</t>
+          <t>8164198217.75183</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>8306.362</t>
+          <t>8828208645.83014</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>8504.72</t>
+          <t>9578965698.69859</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>8661.381</t>
+          <t>9326275353.63531</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>8678.845</t>
+          <t>9513087314.45359</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>8673.975</t>
+          <t>9017124000.39204</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>8234.389</t>
+          <t>8496864942.83204</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>8312.344</t>
+          <t>8671031964.13043</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>8053.287</t>
+          <t>7852480485.30258</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>8065.106</t>
+          <t>8419846365.13637</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>8026.416</t>
+          <t>8078549318.98843</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>7941.661</t>
+          <t>8788713425.81892</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>7590.201</t>
+          <t>9149912423.9445</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6597.374</t>
+          <t>15096.4458046999</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5340.792</t>
+          <t>16587.817834496</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5318.837</t>
+          <t>19346.9250581319</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5616.757</t>
+          <t>18014.6141324864</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5247.205</t>
+          <t>17909.1257786986</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5928.309</t>
+          <t>18757.8564467055</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6097.03</t>
+          <t>18596.931024699</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6078.812</t>
+          <t>19472.9177054153</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6161.091</t>
+          <t>20898.4521756675</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6065.125</t>
+          <t>27497.6359166309</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6073.625</t>
+          <t>25894.3297208261</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6247.562</t>
+          <t>29880.2656663802</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6373.822</t>
+          <t>28405.0908626991</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6570.317</t>
+          <t>25827.1676248396</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6464.209</t>
+          <t>22102.2907013204</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>6247.544</t>
+          <t>24994.4652482995</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>6353.07</t>
+          <t>25631.2081363245</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>6576.149</t>
+          <t>26845.0933964563</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>6599.813</t>
+          <t>24493.6866237499</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>7641.162</t>
+          <t>20620.4868860995</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>7259.067</t>
+          <t>22685.8036930686</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>7327.497</t>
+          <t>18659.8298346962</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>7073.056</t>
+          <t>15877.515294827</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>7059.694</t>
+          <t>13748.9615436288</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>7031.225</t>
+          <t>22042.2360509577</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>6957.5</t>
+          <t>21326.6942746653</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>6625.671</t>
+          <t>21122.0427053761</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18777.75</t>
+          <t>-25935581315.8108</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9679.56</t>
+          <t>-5112021864.58699</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9363.922</t>
+          <t>-4730208136.86242</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9829.145</t>
+          <t>-5222391407.10422</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9433.18</t>
+          <t>-5852390508.12277</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10883.779</t>
+          <t>-6293378244.9949</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10734.728</t>
+          <t>-5888167736.55662</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10471.719</t>
+          <t>-6131584804.74269</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>10254.972</t>
+          <t>-5879061880.0182</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10844.988</t>
+          <t>-6299231504.00325</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>11204.268</t>
+          <t>-6701938978.62294</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>11350.154</t>
+          <t>-6903120885.3572</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>11168.922</t>
+          <t>-6220796094.73677</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>11468.301</t>
+          <t>-7072298586.03703</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10292.197</t>
+          <t>-5661145808.56545</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>9875.212</t>
+          <t>-6462895887.37322</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10884.675</t>
+          <t>-6791219295.67845</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10734.344</t>
+          <t>-6633323327.92672</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>10723.194</t>
+          <t>-6750388650.92983</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>10191.799</t>
+          <t>-6551185290.27965</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>9736.97</t>
+          <t>-6150306724.05105</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>9416.793</t>
+          <t>-6431515927.92774</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>8818.483</t>
+          <t>-5549142931.53028</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>8852.077</t>
+          <t>-6117358989.89325</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>8649.786</t>
+          <t>-5719449522.64803</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>8949.433</t>
+          <t>-6270445497.62736</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>9362.081</t>
+          <t>-6592174037.15191</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>107696.787709755</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>129175.937049907</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>133128.391727487</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>134102.777799839</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>140009.936856051</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>157300.906815727</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>159431.94525684</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>167861.38170927</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>171852.202393442</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>173280.682201334</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>168180.127202924</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>181311.543651482</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>193487.975029578</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>197273.624464092</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>176433.111624171</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>204175.843754096</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>222950.952266396</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>229749.632704465</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>234265.152956604</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>232412.251569056</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>246551.031087828</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>242625.461782878</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>252262.09340083</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>262756.121983005</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>270312.72692587</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>260849.911925432</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>277910.556669371</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>4350.276</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>4567.882</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>4579.921</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>4658.563</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>4273.272</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>4809.218</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4837.664</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>4708.475</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>4752.77</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>4660.697</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>4662.309</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>4790.043</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>4852.018</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>4924.432</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>4843.281</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>4634.178</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>4748.118</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>4806.091</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>4794.609</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>4742.428</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>4549.064</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>4598.724</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>4433.977</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>4508.912</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>4451.371</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>4481.164</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>4341.646</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>165107.567166635</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>195358.649371439</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>193638.076023315</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>198695.245091172</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>205151.217551965</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>239264.834649256</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>254868.811806479</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>266564.005415377</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>262831.819109374</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>259606.085282976</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>259963.607811728</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>276084.421367692</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>297523.501222171</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>293648.126715897</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>268907.982843353</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>300200.090575927</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>345977.434473723</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>356691.090741492</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>366070.753687939</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>354769.713455252</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>384188.584200031</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>378677.624032812</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>392247.809770849</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>418553.799968068</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>424784.019598538</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>404474.415715241</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>441509.956585209</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>13253.056</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>4466.521</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>4166.343</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>4279.383</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>4343.732</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>4879.781</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5412.45</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>5458.496</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>5011.027</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>4818.357</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>4973.78</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>4762.24</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>4423.52</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>5034.659</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>4534.888</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>4111.25</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>4647.072</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>4887.42</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>4701.682</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>4784.084</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>4862.489</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>4625.365</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>4263.611</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>5223.022</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>5176.543</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>5095.45</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>5368.26</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-50.22</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>19.57</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>27.66</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>21.49</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12.65</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>11.36</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>22.11</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>31.19</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>44.09</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>42.54</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>51.96</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>34.55</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>40.37</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>59.72</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>49.29</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>58.42</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>65.89</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>35.16</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>35.83</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>36.54</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>23.42</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>356.776</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>29403431.004</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>6.327</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>7.442</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>1289.109</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>5.617</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5.92</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>426.802</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>5.182</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>888.091</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>4.561</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>1216.108</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>4.351</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>4.363</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>3.573</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>3.488</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>3.407</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>3.436</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>3.441</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>3.315</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2.915</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>2.595</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2.399</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>2.556</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2.789</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>118059.900410288</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>121739.123013322</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>130121.634706223</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>127256.76523981</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>137706.201514476</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>146660.585951793</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>109971.058125267</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>114439.328466162</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>133174.306738761</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>159289.374350964</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>166676.468369448</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>178251.897034174</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>187208.506968019</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>176072.928652141</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>146666.35696545</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>201286.818284291</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>204376.79604213</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>219027.55953673</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>223542.26346724</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>226481.364844066</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>213709.367891703</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>236256.394861193</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>240469.87803612</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>208994.29018096</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>208768.681746139</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>226023.996076857</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>215651.399605853</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6597374320.34105</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5340792000.0003</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5318836999.99843</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5616756999.99844</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>5247204999.99971</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5928309000.00095</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6097030000.0021</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6078812000.00074</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6161090999.99878</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6065124999.99957</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6073624999.99818</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6247561999.99848</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6373821999.99891</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6570316999.99905</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6464209000.00093</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>6247543999.99998</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>6353070000.00239</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>6576149000.00036</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>6599813000.00131</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>7641162201.45904</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>7259067031.44633</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>7327497377.12862</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>7073056260.50807</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>7059693712.11491</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>7031224689.29986</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>6957500205.41989</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>6625671463.7823</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7598077022.19168</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>7501043999.9998</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>7472930999.99861</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>7766792999.99893</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>7247423000.00048</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>8082817000.00206</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8273316000.0015</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8179094000.00069</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>8281618999.99972</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>8089403000.00036</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>8116306999.99939</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8426405999.99876</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>8579603999.99801</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>8780299000.00047</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8571183000.00138</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8306362000.00134</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8504720000.0037</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>8661381000.00022</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>8678845000.00138</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>8673974808.99018</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>8234388899.31017</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>8312343904.74769</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>8053286863.69826</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>8065106327.83316</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>8026416027.92743</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>7941661193.69262</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>7590200748.00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4350276248.42139</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4567881756.77234</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4579920619.57635</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4658562574.22012</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4273272034.04765</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4809218385.27428</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4837663679.3448</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4708475464.77087</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4752769955.4423</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4660696757.37294</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4662308544.91117</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4790042669.01857</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4852017747.11251</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4924432320.37268</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4843281370.33485</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4634178313.16057</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4748117928.09568</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>4806091093.38963</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4794608554.45546</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>4742428009.12554</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>4549064397.28838</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>4598724052.19878</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>4433976575.64493</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>4508912466.54464</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>4451371144.68868</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>4481163728.41522</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>4341645938.59492</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3994661.9112242</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4203199.99999982</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4138699.99999897</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4062800.00000029</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3986700.00000036</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4205599.99999982</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4285500.00000015</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4492300.0000007</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4502399.99999934</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4505000.00000065</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4461500.00000027</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4477599.99999931</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4571100.00000148</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4680400.00000058</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4572199.99999896</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4483900.00000074</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4511200.00000019</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4603699.99999996</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>4631299.99999913</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4623718.11947782</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>4377689.38885488</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>4403962.09625447</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>4253550.56664217</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>4242281.58357038</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>4213429.92170953</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>4154396.96102212</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>3953649.35251211</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3537306.77707062</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3685299.99999977</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3631999.99999891</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3585900.00000032</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3523800.00000047</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3721699.99999998</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3808200.00000019</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4009600.00000054</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4017099.99999926</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4035300.00000069</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3991800.0000003</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3992599.99999924</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4080100.00000145</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4183400.00000056</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4095399.999999</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>4004800.00000076</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>4016000.00000024</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>4124599.99999998</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>4147199.99999906</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>4142906.04849409</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>3924004.41567433</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>3946198.81694653</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>3798620.36906162</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>3775865.76864951</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>3749757.26923105</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>3696342.77688602</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3507706.96427656</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7598077022.19168</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>7501043999.9998</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>7472930999.99861</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>7766792999.99893</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>7247423000.00048</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8082817000.00206</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8273316000.0015</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8179094000.00069</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>8281618999.99972</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>8089403000.00036</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>8116306999.99939</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>8426405999.99876</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>8579603999.99801</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>8780299000.00047</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>8571183000.00138</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>8306362000.00134</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>8504720000.0037</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>8661381000.00022</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>8678845000.00138</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>8673974808.99018</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>8234388899.31017</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>8312343904.74769</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>8053286863.69826</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>8065106327.83316</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>8026416027.92743</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>7941661193.69262</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>7590200748.00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6597374320.34105</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5340792000.0003</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>5318836999.99843</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5616756999.99844</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>5247204999.99971</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5928309000.00095</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6097030000.0021</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>6078812000.00074</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6161090999.99878</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6065124999.99957</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6073624999.99818</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6247561999.99848</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6373821999.99891</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6570316999.99905</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6464209000.00093</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>6247543999.99998</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>6353070000.00239</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>6576149000.00036</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>6599813000.00131</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>7641162201.45904</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>7259067031.44633</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>7327497377.12862</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>7073056260.50807</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>7059693712.11491</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>7031224689.29986</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>6957500205.41989</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>6625671463.7823</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>535909.251903209</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>603993.323603591</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>631112.643250877</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>649995.301396762</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>688574.210477393</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>776128.547568127</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>744146.854235163</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>778011.145170323</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>802457.321187352</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>836168.365335492</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>875789.122998184</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>940971.269736614</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1006290.45279449</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>973244.129157025</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>842237.920701493</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1013810.42013432</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1112597.34612111</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1173029.4895619</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1183616.80605351</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1159791.36393044</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>1202634.26524415</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1219231.12052387</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>1261166.17844233</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1263981.21570293</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1273161.24010873</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1281280.6652979</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1321169.80675111</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>182517.490000644</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>216214.428284647</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>217664.653582738</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>228026.055508953</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>240511.084635492</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>271893.466428816</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>288102.393238667</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>300620.590774071</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>301534.779630259</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>296078.941511846</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>297012.355450662</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>317353.137226475</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>339998.727849272</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>341633.286004256</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>313655.576488803</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>348793.223615453</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>402216.32275118</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>413439.02365731</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>426353.792175192</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>417818.730415725</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>455877.510530322</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>448922.836141996</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>463903.29817032</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>482761.64579129</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>488706.972146397</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>481648.751875418</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>506535.716406962</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
